--- a/testdata/realdata/ports.xlsx
+++ b/testdata/realdata/ports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
           <t>日期</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>所属板卡</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -555,6 +560,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -623,6 +633,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -691,6 +706,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,6 +779,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -827,6 +852,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -895,6 +925,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>BRD-DEV-279116876-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -963,6 +998,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244077958-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1031,6 +1071,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244077958-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1099,6 +1144,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244077958-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1167,6 +1217,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244077958-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1235,6 +1290,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244077958-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1303,6 +1363,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244077958-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1371,6 +1436,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1439,6 +1509,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1507,6 +1582,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1575,6 +1655,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1643,6 +1728,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1711,6 +1801,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081515-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1783,6 +1878,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>BRD-DEV-1727803072-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1855,6 +1955,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>BRD-DEV-1727803072-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1927,6 +2032,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>BRD-DEV-1727803072-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1999,6 +2109,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>BRD-DEV-1727803072-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2071,6 +2186,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>BRD-DEV-1727803072-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2143,6 +2263,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>BRD-DEV-1727803072-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2211,6 +2336,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2279,6 +2409,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2347,6 +2482,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2415,6 +2555,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2483,6 +2628,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2551,6 +2701,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>BRD-DEV-469656125-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2619,6 +2774,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2687,6 +2847,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2755,6 +2920,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2823,6 +2993,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2891,6 +3066,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2959,6 +3139,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>BRD-DEV-678337697-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3027,6 +3212,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3095,6 +3285,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3163,6 +3358,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3231,6 +3431,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3299,6 +3504,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3367,6 +3577,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>BRD-DEV-962010355-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3435,6 +3650,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3503,6 +3723,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3571,6 +3796,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3639,6 +3869,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3707,6 +3942,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3775,6 +4015,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>BRD-DEV-280162986-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3843,6 +4088,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3911,6 +4161,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3979,6 +4234,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4047,6 +4307,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4115,6 +4380,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4183,6 +4453,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>BRD-DEV-4059698545-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4251,6 +4526,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4319,6 +4599,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4387,6 +4672,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4455,6 +4745,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4523,6 +4818,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4591,6 +4891,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>BRD-DEV-304758391-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4663,6 +4968,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4735,6 +5045,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4807,6 +5122,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4879,6 +5199,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4951,6 +5276,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5023,6 +5353,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>BRD-DEV-6359892789-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5091,6 +5426,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5159,6 +5499,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5227,6 +5572,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5295,6 +5645,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5363,6 +5718,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5431,6 +5791,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081815-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5499,6 +5864,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5567,6 +5937,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5635,6 +6010,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5703,6 +6083,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5771,6 +6156,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5839,6 +6229,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244082251-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5907,6 +6302,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5975,6 +6375,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6043,6 +6448,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6111,6 +6521,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6179,6 +6594,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6247,6 +6667,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>BRD-DEV-244081526-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6315,6 +6740,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6383,6 +6813,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-01-02</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6451,6 +6886,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6519,6 +6959,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-02-01</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6587,6 +7032,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-02-02</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6653,6 +7103,11 @@
       <c r="N91" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>BRD-DEV-502220401-02-01</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/ports.xlsx
+++ b/testdata/realdata/ports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,11 @@
           <t>所属板卡</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>所属VPN实例</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -565,6 +570,11 @@
           <t>BRD-DEV-279116876-01-01</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -638,6 +648,11 @@
           <t>BRD-DEV-279116876-01-02</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -711,6 +726,11 @@
           <t>BRD-DEV-279116876-01-01</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -784,6 +804,11 @@
           <t>BRD-DEV-279116876-02-01</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -857,6 +882,11 @@
           <t>BRD-DEV-279116876-02-02</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -930,6 +960,11 @@
           <t>BRD-DEV-279116876-02-01</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1003,6 +1038,11 @@
           <t>BRD-DEV-244077958-01-01</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1076,6 +1116,11 @@
           <t>BRD-DEV-244077958-01-02</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1149,6 +1194,11 @@
           <t>BRD-DEV-244077958-01-01</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1222,6 +1272,11 @@
           <t>BRD-DEV-244077958-02-01</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1295,6 +1350,11 @@
           <t>BRD-DEV-244077958-02-02</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1368,6 +1428,11 @@
           <t>BRD-DEV-244077958-02-01</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1441,6 +1506,11 @@
           <t>BRD-DEV-244081515-01-01</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1514,6 +1584,11 @@
           <t>BRD-DEV-244081515-01-02</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1587,6 +1662,11 @@
           <t>BRD-DEV-244081515-01-01</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1660,6 +1740,11 @@
           <t>BRD-DEV-244081515-02-01</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1733,6 +1818,11 @@
           <t>BRD-DEV-244081515-02-02</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1806,6 +1896,11 @@
           <t>BRD-DEV-244081515-02-01</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1883,6 +1978,11 @@
           <t>BRD-DEV-1727803072-01-01</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1960,6 +2060,11 @@
           <t>BRD-DEV-1727803072-01-02</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2037,6 +2142,11 @@
           <t>BRD-DEV-1727803072-01-01</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2114,6 +2224,11 @@
           <t>BRD-DEV-1727803072-02-01</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2191,6 +2306,11 @@
           <t>BRD-DEV-1727803072-02-02</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2268,6 +2388,11 @@
           <t>BRD-DEV-1727803072-02-01</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2341,6 +2466,11 @@
           <t>BRD-DEV-469656125-01-01</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2414,6 +2544,11 @@
           <t>BRD-DEV-469656125-01-02</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2487,6 +2622,11 @@
           <t>BRD-DEV-469656125-01-01</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2560,6 +2700,11 @@
           <t>BRD-DEV-469656125-02-01</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2633,6 +2778,11 @@
           <t>BRD-DEV-469656125-02-02</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2706,6 +2856,11 @@
           <t>BRD-DEV-469656125-02-01</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2779,6 +2934,11 @@
           <t>BRD-DEV-678337697-01-01</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2852,6 +3012,11 @@
           <t>BRD-DEV-678337697-01-02</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2925,6 +3090,11 @@
           <t>BRD-DEV-678337697-01-01</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2998,6 +3168,11 @@
           <t>BRD-DEV-678337697-02-01</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3071,6 +3246,11 @@
           <t>BRD-DEV-678337697-02-02</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3144,6 +3324,11 @@
           <t>BRD-DEV-678337697-02-01</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3217,6 +3402,11 @@
           <t>BRD-DEV-962010355-01-01</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3290,6 +3480,11 @@
           <t>BRD-DEV-962010355-01-02</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3363,6 +3558,11 @@
           <t>BRD-DEV-962010355-01-01</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3436,6 +3636,11 @@
           <t>BRD-DEV-962010355-02-01</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3509,6 +3714,11 @@
           <t>BRD-DEV-962010355-02-02</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3582,6 +3792,11 @@
           <t>BRD-DEV-962010355-02-01</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3655,6 +3870,11 @@
           <t>BRD-DEV-280162986-01-01</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3728,6 +3948,11 @@
           <t>BRD-DEV-280162986-01-02</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3801,6 +4026,11 @@
           <t>BRD-DEV-280162986-01-01</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3874,6 +4104,11 @@
           <t>BRD-DEV-280162986-02-01</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3947,6 +4182,11 @@
           <t>BRD-DEV-280162986-02-02</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4020,6 +4260,11 @@
           <t>BRD-DEV-280162986-02-01</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4093,6 +4338,11 @@
           <t>BRD-DEV-4059698545-01-01</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4166,6 +4416,11 @@
           <t>BRD-DEV-4059698545-01-02</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4239,6 +4494,11 @@
           <t>BRD-DEV-4059698545-01-01</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4312,6 +4572,11 @@
           <t>BRD-DEV-4059698545-02-01</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4385,6 +4650,11 @@
           <t>BRD-DEV-4059698545-02-02</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4458,6 +4728,11 @@
           <t>BRD-DEV-4059698545-02-01</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4531,6 +4806,11 @@
           <t>BRD-DEV-304758391-01-01</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4604,6 +4884,11 @@
           <t>BRD-DEV-304758391-01-02</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4677,6 +4962,11 @@
           <t>BRD-DEV-304758391-01-01</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4750,6 +5040,11 @@
           <t>BRD-DEV-304758391-02-01</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4823,6 +5118,11 @@
           <t>BRD-DEV-304758391-02-02</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4896,6 +5196,11 @@
           <t>BRD-DEV-304758391-02-01</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4973,6 +5278,11 @@
           <t>BRD-DEV-6359892789-01-01</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5050,6 +5360,11 @@
           <t>BRD-DEV-6359892789-01-02</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5127,6 +5442,11 @@
           <t>BRD-DEV-6359892789-01-01</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5204,6 +5524,11 @@
           <t>BRD-DEV-6359892789-02-01</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5281,6 +5606,11 @@
           <t>BRD-DEV-6359892789-02-02</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5358,6 +5688,11 @@
           <t>BRD-DEV-6359892789-02-01</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5431,6 +5766,11 @@
           <t>BRD-DEV-244081815-01-01</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5504,6 +5844,11 @@
           <t>BRD-DEV-244081815-01-02</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5577,6 +5922,11 @@
           <t>BRD-DEV-244081815-01-01</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5650,6 +6000,11 @@
           <t>BRD-DEV-244081815-02-01</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5723,6 +6078,11 @@
           <t>BRD-DEV-244081815-02-02</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5796,6 +6156,11 @@
           <t>BRD-DEV-244081815-02-01</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5869,6 +6234,11 @@
           <t>BRD-DEV-244082251-01-01</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5942,6 +6312,11 @@
           <t>BRD-DEV-244082251-01-02</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6015,6 +6390,11 @@
           <t>BRD-DEV-244082251-01-01</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6088,6 +6468,11 @@
           <t>BRD-DEV-244082251-02-01</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6161,6 +6546,11 @@
           <t>BRD-DEV-244082251-02-02</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6234,6 +6624,11 @@
           <t>BRD-DEV-244082251-02-01</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>L3VPN-001</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6307,6 +6702,11 @@
           <t>BRD-DEV-244081526-01-01</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6380,6 +6780,11 @@
           <t>BRD-DEV-244081526-01-02</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6453,6 +6858,11 @@
           <t>BRD-DEV-244081526-01-01</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6526,6 +6936,11 @@
           <t>BRD-DEV-244081526-02-01</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6599,6 +7014,11 @@
           <t>BRD-DEV-244081526-02-02</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6672,6 +7092,11 @@
           <t>BRD-DEV-244081526-02-01</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>L3VPN-002</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6745,6 +7170,11 @@
           <t>BRD-DEV-502220401-01-01</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6818,6 +7248,11 @@
           <t>BRD-DEV-502220401-01-02</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6891,6 +7326,11 @@
           <t>BRD-DEV-502220401-01-01</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6964,6 +7404,11 @@
           <t>BRD-DEV-502220401-02-01</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7037,6 +7482,11 @@
           <t>BRD-DEV-502220401-02-02</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7108,6 +7558,11 @@
       <c r="O91" t="inlineStr">
         <is>
           <t>BRD-DEV-502220401-02-01</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>L3VPN-003</t>
         </is>
       </c>
     </row>
